--- a/data/excel/buffs.xlsx
+++ b/data/excel/buffs.xlsx
@@ -42,8 +42,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C0504D"/>
-        <bgColor rgb="00C0504D"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -441,15 +442,15 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,245 +501,259 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>中毒</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>poison</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/poison_fx.tscn</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>燃烧</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>burn</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/burn_fx.tscn</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>冰冻</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>freeze</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/freeze_fx.tscn</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>麻痹</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>paralysis</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/paralysis_fx.tscn</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>无敌</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>invincible</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/invincible_fx.tscn</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>1006</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>眩晕</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>stun</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>res://scenes/effects/stun_fx.tscn</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>1007</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>减速</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>slow</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="n">
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I8"/>
